--- a/RFQ Generator Beta Version/Templates/OP TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/OP TEMPLATE.xlsx
@@ -5,19 +5,19 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\bin\Debug\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF06D0C-75BB-4132-9372-18B2021E79AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274897ED-B03F-4048-A87D-7BC8D1D8D676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3B819F4F-66F1-4659-9300-3F5ADAC4BEAE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2DA8C3B9-7BBA-43E4-97CE-AECDC4D9C533}"/>
   </bookViews>
   <sheets>
     <sheet name="COMMERCIAL." sheetId="32" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'COMMERCIAL.'!$A$1:$H$60</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'COMMERCIAL.'!$1:$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'COMMERCIAL.'!$A$1:$H$55</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'COMMERCIAL.'!$1:$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -96,12 +96,12 @@
     <t>E-MAIL: orbitperkasa@gmail.com</t>
   </si>
   <si>
-    <t>60 DAYS</t>
-  </si>
-  <si>
     <t>ORBIT PERKASA SDN BHD</t>
   </si>
   <si>
+    <t>30 DAYS</t>
+  </si>
+  <si>
     <t>Remarks:-</t>
   </si>
   <si>
@@ -111,33 +111,36 @@
     <t>2) Price quoted is based on quantity required. Any changes in quantity is subject to requote.</t>
   </si>
   <si>
+    <t>3) 10% of PO value will be charged upon late payment from the invoice date after 60 days</t>
+  </si>
+  <si>
+    <t>TEL: 085-326526</t>
+  </si>
+  <si>
     <t>UNIT 3,05 3RD FLOOR</t>
   </si>
   <si>
-    <t>WISMA PEKITA TUNKU JALAN PADANG</t>
+    <t>WISMA PELITA TUNKU JALAN PADANG</t>
   </si>
   <si>
     <t>98000 MIRI SARAWAK</t>
   </si>
   <si>
-    <t>TEL: 085-326526</t>
+    <t>Prepared For</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>Your RFQ</t>
+  </si>
+  <si>
+    <t>Our Ref</t>
   </si>
   <si>
     <t>client_name</t>
   </si>
   <si>
-    <t>Prepared For</t>
-  </si>
-  <si>
-    <t>DATE</t>
-  </si>
-  <si>
-    <t>Your RFQ</t>
-  </si>
-  <si>
-    <t>Our Ref</t>
-  </si>
-  <si>
     <t>_date</t>
   </si>
   <si>
@@ -147,6 +150,12 @@
     <t>quote_code</t>
   </si>
   <si>
+    <t>Price(RM)</t>
+  </si>
+  <si>
+    <t>Sub Total (RM)</t>
+  </si>
+  <si>
     <t>_num</t>
   </si>
   <si>
@@ -162,40 +171,31 @@
     <t>unit_price</t>
   </si>
   <si>
+    <t>sub_total</t>
+  </si>
+  <si>
     <t>total_price</t>
   </si>
   <si>
+    <t>SUBTOTAL</t>
+  </si>
+  <si>
+    <t>DISCOUNT</t>
+  </si>
+  <si>
+    <t>_discount</t>
+  </si>
+  <si>
     <t>summary_total_price</t>
   </si>
   <si>
-    <t>DISCOUNT</t>
-  </si>
-  <si>
-    <t>SUB TOTAL</t>
-  </si>
-  <si>
-    <t>sub_total</t>
-  </si>
-  <si>
-    <t>_discount</t>
-  </si>
-  <si>
-    <t>3) 10% of PO value will be charged upon late payment from the invoice date after validity</t>
-  </si>
-  <si>
     <t>_validity</t>
   </si>
   <si>
+    <t>delivery_point</t>
+  </si>
+  <si>
     <t>delivery_term</t>
-  </si>
-  <si>
-    <t>delivery_point</t>
-  </si>
-  <si>
-    <t>Price (RM)</t>
-  </si>
-  <si>
-    <t>Total (RM)</t>
   </si>
 </sst>
 </file>
@@ -271,7 +271,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -366,50 +366,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -462,7 +418,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -481,9 +437,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -497,86 +451,117 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="5" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="5" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{93E173E9-E6B2-436D-B9CA-05B73F796A02}"/>
-    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{FDF557B0-2525-4D44-B1D4-C58C3C556510}"/>
-    <cellStyle name="Normal 3" xfId="4" xr:uid="{C5F44040-F370-4CD3-9FA0-D2EAA5D265F0}"/>
-    <cellStyle name="Normal 3 2" xfId="5" xr:uid="{03264213-81A5-499C-B9E9-71CDF0D44EBE}"/>
-    <cellStyle name="Normal 4" xfId="6" xr:uid="{6611FED4-50C0-4D56-B698-D8CD062CF0F6}"/>
-    <cellStyle name="Normal 5" xfId="7" xr:uid="{4A34D188-ACDA-4BF5-9434-B3EE1F6EE5DC}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{915A4D4D-05E3-4DF7-8BEB-2847CE172A7E}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{8D8EFCF1-FB14-4E75-A167-9EBCA08E9B3C}"/>
+    <cellStyle name="Normal 3" xfId="4" xr:uid="{0F29CA40-F26C-46C7-8461-A756CC58AAE1}"/>
+    <cellStyle name="Normal 3 2" xfId="5" xr:uid="{79356F39-4733-4E23-A4F3-2D46CFFF8403}"/>
+    <cellStyle name="Normal 4" xfId="6" xr:uid="{CC680972-FA1F-4C0E-AE8F-CEFA7830A03D}"/>
+    <cellStyle name="Normal 5" xfId="7" xr:uid="{18EC9484-F37B-466C-99B4-7EDDE92F4867}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -608,10 +593,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1120" name="Picture 1" descr="orbit">
+        <xdr:cNvPr id="1230" name="Picture 1" descr="orbit">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F6AD902-C480-A96F-4373-A6B68DC9C597}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECE79515-22FC-4A56-B24A-246F2A0F5AC6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -671,21 +656,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>144780</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1121" name="Picture 3">
+        <xdr:cNvPr id="1231" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D16DD77C-7482-11BB-C713-AAAC34B7A7E3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54E5898B-F9D1-A632-44C9-464BE96F7839}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -708,7 +693,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="144780" y="11574780"/>
+          <a:off x="144780" y="10050780"/>
           <a:ext cx="1089660" cy="769620"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1030,19 +1015,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C82EFF89-8595-49F2-9604-8781EE90C9F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1991A9DC-37E5-4BE6-A90B-E8557E5F8471}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AW152"/>
+  <dimension ref="A1:AW157"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" style="2" customWidth="1"/>
     <col min="2" max="2" width="27" style="2" customWidth="1"/>
     <col min="3" max="3" width="2.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="49.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.21875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="51.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" style="1" customWidth="1"/>
     <col min="9" max="9" width="14.6640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="2.33203125" style="2" customWidth="1"/>
     <col min="11" max="18" width="9.109375" style="2" hidden="1" customWidth="1"/>
@@ -1058,7 +1043,7 @@
     <col min="50" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="F1" s="1"/>
@@ -1099,17 +1084,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:44" ht="26.25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:49" ht="26.25" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="D2" s="17" t="s">
-        <v>20</v>
+      <c r="D2" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="43" t="s">
+      <c r="G2" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="43"/>
+      <c r="H2" s="31"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -1145,11 +1130,11 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="3" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1"/>
       <c r="M3" s="1"/>
@@ -1187,11 +1172,11 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F4" s="1"/>
       <c r="M4" s="1"/>
@@ -1227,11 +1212,11 @@
       <c r="AQ4" s="1"/>
       <c r="AR4" s="3"/>
     </row>
-    <row r="5" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F5" s="1"/>
       <c r="M5" s="1"/>
@@ -1267,7 +1252,7 @@
       <c r="AQ5" s="1"/>
       <c r="AR5" s="3"/>
     </row>
-    <row r="6" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="F6" s="1"/>
@@ -1304,11 +1289,11 @@
       <c r="AQ6" s="1"/>
       <c r="AR6" s="3"/>
     </row>
-    <row r="7" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="D7" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1"/>
       <c r="M7" s="1"/>
@@ -1344,7 +1329,7 @@
       <c r="AQ7" s="1"/>
       <c r="AR7" s="3"/>
     </row>
-    <row r="8" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="D8" s="2" t="s">
@@ -1384,7 +1369,7 @@
       <c r="AQ8" s="1"/>
       <c r="AR8" s="3"/>
     </row>
-    <row r="9" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="F9" s="1"/>
@@ -1421,7 +1406,7 @@
       <c r="AQ9" s="1"/>
       <c r="AR9" s="3"/>
     </row>
-    <row r="10" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="F10" s="1"/>
@@ -1458,25 +1443,25 @@
       <c r="AQ10" s="1"/>
       <c r="AR10" s="3"/>
     </row>
-    <row r="11" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="17" t="s">
         <v>30</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -1511,16 +1496,16 @@
       <c r="AQ11" s="1"/>
       <c r="AR11" s="3"/>
     </row>
-    <row r="12" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="17" t="s">
         <v>31</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -1555,16 +1540,17 @@
       <c r="AQ12" s="1"/>
       <c r="AR12" s="3"/>
     </row>
-    <row r="13" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
-      <c r="E13" s="26" t="s">
+      <c r="B13" s="3"/>
+      <c r="E13" s="17" t="s">
         <v>32</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -1599,9 +1585,18 @@
       <c r="AQ13" s="1"/>
       <c r="AR13" s="3"/>
     </row>
-    <row r="14" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
       <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -1633,11 +1628,25 @@
       <c r="AO14" s="1"/>
       <c r="AP14" s="1"/>
       <c r="AQ14" s="1"/>
-      <c r="AR14" s="3"/>
-    </row>
-    <row r="15" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AR14" s="1"/>
+      <c r="AS14" s="1"/>
+      <c r="AT14" s="1"/>
+      <c r="AU14" s="1"/>
+      <c r="AV14" s="1"/>
+      <c r="AW14" s="1"/>
+    </row>
+    <row r="15" spans="1:49" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
       <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -1669,542 +1678,420 @@
       <c r="AO15" s="1"/>
       <c r="AP15" s="1"/>
       <c r="AQ15" s="1"/>
-      <c r="AR15" s="3"/>
-    </row>
-    <row r="16" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="1"/>
-      <c r="B16" s="3"/>
-      <c r="F16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-      <c r="Z16" s="1"/>
-      <c r="AA16" s="1"/>
-      <c r="AB16" s="1"/>
-      <c r="AC16" s="1"/>
-      <c r="AD16" s="1"/>
-      <c r="AE16" s="1"/>
-      <c r="AF16" s="1"/>
-      <c r="AG16" s="1"/>
-      <c r="AH16" s="1"/>
-      <c r="AI16" s="1"/>
-      <c r="AJ16" s="1"/>
-      <c r="AK16" s="1"/>
-      <c r="AL16" s="1"/>
-      <c r="AM16" s="1"/>
-      <c r="AN16" s="1"/>
-      <c r="AO16" s="1"/>
-      <c r="AP16" s="1"/>
-      <c r="AQ16" s="1"/>
-      <c r="AR16" s="3"/>
-    </row>
-    <row r="17" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
-      <c r="Z17" s="1"/>
-      <c r="AA17" s="1"/>
-      <c r="AB17" s="1"/>
-      <c r="AC17" s="1"/>
-      <c r="AD17" s="1"/>
-      <c r="AE17" s="1"/>
-      <c r="AF17" s="1"/>
-      <c r="AG17" s="1"/>
-      <c r="AH17" s="1"/>
-      <c r="AI17" s="1"/>
-      <c r="AJ17" s="1"/>
-      <c r="AK17" s="1"/>
-      <c r="AL17" s="1"/>
-      <c r="AM17" s="1"/>
-      <c r="AN17" s="1"/>
-      <c r="AO17" s="1"/>
-      <c r="AP17" s="1"/>
-      <c r="AQ17" s="1"/>
-      <c r="AR17" s="1"/>
-      <c r="AS17" s="1"/>
-      <c r="AT17" s="1"/>
-      <c r="AU17" s="1"/>
-      <c r="AV17" s="1"/>
-      <c r="AW17" s="1"/>
-    </row>
-    <row r="18" spans="1:49" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-      <c r="Z18" s="1"/>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
-      <c r="AD18" s="1"/>
-      <c r="AE18" s="1"/>
-      <c r="AF18" s="1"/>
-      <c r="AG18" s="1"/>
-      <c r="AH18" s="1"/>
-      <c r="AI18" s="1"/>
-      <c r="AJ18" s="1"/>
-      <c r="AK18" s="1"/>
-      <c r="AL18" s="1"/>
-      <c r="AM18" s="1"/>
-      <c r="AN18" s="1"/>
-      <c r="AO18" s="1"/>
-      <c r="AP18" s="1"/>
-      <c r="AQ18" s="1"/>
-      <c r="AR18" s="1"/>
-      <c r="AS18" s="1"/>
-      <c r="AT18" s="1"/>
-      <c r="AU18" s="1"/>
-      <c r="AV18" s="1"/>
-      <c r="AW18" s="1"/>
-    </row>
-    <row r="19" spans="1:49" s="5" customFormat="1" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="44" t="s">
+      <c r="AR15" s="1"/>
+      <c r="AS15" s="1"/>
+      <c r="AT15" s="1"/>
+      <c r="AU15" s="1"/>
+      <c r="AV15" s="1"/>
+      <c r="AW15" s="1"/>
+    </row>
+    <row r="16" spans="1:49" s="5" customFormat="1" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4"/>
-      <c r="AB19" s="4"/>
-      <c r="AC19" s="4"/>
-      <c r="AD19" s="4"/>
-      <c r="AE19" s="4"/>
-      <c r="AF19" s="4"/>
-      <c r="AG19" s="4"/>
-      <c r="AH19" s="4"/>
-      <c r="AI19" s="4"/>
-      <c r="AJ19" s="4"/>
-      <c r="AK19" s="4"/>
-      <c r="AL19" s="4"/>
-      <c r="AM19" s="4"/>
-      <c r="AN19" s="4"/>
-      <c r="AO19" s="4"/>
-      <c r="AP19" s="4"/>
-      <c r="AQ19" s="4"/>
-      <c r="AR19" s="4"/>
-      <c r="AS19" s="4"/>
-      <c r="AT19" s="4"/>
-      <c r="AU19" s="4"/>
-      <c r="AV19" s="4"/>
-      <c r="AW19" s="4"/>
-    </row>
-    <row r="20" spans="1:49" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6"/>
-      <c r="T20" s="6"/>
-      <c r="U20" s="6"/>
-      <c r="V20" s="6"/>
-      <c r="W20" s="6"/>
-      <c r="X20" s="6"/>
-      <c r="Y20" s="6"/>
-      <c r="Z20" s="6"/>
-      <c r="AA20" s="6"/>
-      <c r="AB20" s="6"/>
-      <c r="AC20" s="6"/>
-      <c r="AD20" s="6"/>
-      <c r="AE20" s="6"/>
-      <c r="AF20" s="6"/>
-      <c r="AG20" s="6"/>
-      <c r="AH20" s="6"/>
-      <c r="AI20" s="6"/>
-      <c r="AJ20" s="6"/>
-      <c r="AK20" s="6"/>
-      <c r="AL20" s="6"/>
-      <c r="AM20" s="6"/>
-      <c r="AN20" s="6"/>
-      <c r="AO20" s="6"/>
-      <c r="AP20" s="6"/>
-      <c r="AQ20" s="6"/>
-      <c r="AR20" s="6"/>
-      <c r="AS20" s="6"/>
-      <c r="AT20" s="6"/>
-      <c r="AU20" s="6"/>
-      <c r="AV20" s="6"/>
-      <c r="AW20" s="6"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="4"/>
+      <c r="AA16" s="4"/>
+      <c r="AB16" s="4"/>
+      <c r="AC16" s="4"/>
+      <c r="AD16" s="4"/>
+      <c r="AE16" s="4"/>
+      <c r="AF16" s="4"/>
+      <c r="AG16" s="4"/>
+      <c r="AH16" s="4"/>
+      <c r="AI16" s="4"/>
+      <c r="AJ16" s="4"/>
+      <c r="AK16" s="4"/>
+      <c r="AL16" s="4"/>
+      <c r="AM16" s="4"/>
+      <c r="AN16" s="4"/>
+      <c r="AO16" s="4"/>
+      <c r="AP16" s="4"/>
+      <c r="AQ16" s="4"/>
+      <c r="AR16" s="4"/>
+      <c r="AS16" s="4"/>
+      <c r="AT16" s="4"/>
+      <c r="AU16" s="4"/>
+      <c r="AV16" s="4"/>
+      <c r="AW16" s="4"/>
+    </row>
+    <row r="17" spans="1:49" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="6"/>
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="6"/>
+      <c r="AB17" s="6"/>
+      <c r="AC17" s="6"/>
+      <c r="AD17" s="6"/>
+      <c r="AE17" s="6"/>
+      <c r="AF17" s="6"/>
+      <c r="AG17" s="6"/>
+      <c r="AH17" s="6"/>
+      <c r="AI17" s="6"/>
+      <c r="AJ17" s="6"/>
+      <c r="AK17" s="6"/>
+      <c r="AL17" s="6"/>
+      <c r="AM17" s="6"/>
+      <c r="AN17" s="6"/>
+      <c r="AO17" s="6"/>
+      <c r="AP17" s="6"/>
+      <c r="AQ17" s="6"/>
+      <c r="AR17" s="6"/>
+      <c r="AS17" s="6"/>
+      <c r="AT17" s="6"/>
+      <c r="AU17" s="6"/>
+      <c r="AV17" s="6"/>
+      <c r="AW17" s="6"/>
+    </row>
+    <row r="18" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="7"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="9"/>
+    </row>
+    <row r="19" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A19" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="11"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="13"/>
     </row>
     <row r="21" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="7"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="11"/>
-    </row>
-    <row r="22" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="28" t="s">
+      <c r="A21" s="14"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="27"/>
+    </row>
+    <row r="22" spans="1:49" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="46"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="H22" s="25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="11"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="21"/>
+    </row>
+    <row r="24" spans="1:49" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="16"/>
+      <c r="B24" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="10"/>
+      <c r="B25" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="11"/>
+      <c r="B26" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="52" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="17"/>
+      <c r="B37" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="17">
         <v>1</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="17">
         <v>2</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="28" t="s">
+      <c r="B39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="17">
         <v>3</v>
       </c>
-      <c r="F22" s="29" t="s">
+      <c r="B40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="17">
         <v>4</v>
       </c>
-      <c r="G22" s="28" t="s">
+      <c r="B41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="15"/>
+    </row>
+    <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="17">
+        <v>5</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H22" s="28" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="15"/>
-    </row>
-    <row r="24" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="16"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="11"/>
-    </row>
-    <row r="25" spans="1:49" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="41"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G25" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="H25" s="31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="18"/>
-      <c r="B26" s="37"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="33"/>
-    </row>
-    <row r="27" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="20"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="34"/>
-    </row>
-    <row r="28" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="12"/>
-      <c r="B28" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="G28" s="35"/>
-      <c r="H28" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="12"/>
-      <c r="B29" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="G29" s="35"/>
-      <c r="H29" s="12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="12"/>
-      <c r="B30" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="G30" s="35"/>
-      <c r="H30" s="36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:49" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="21"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="25"/>
-    </row>
-    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="26"/>
-      <c r="B44" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="E42" s="15"/>
+    </row>
+    <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="17"/>
+      <c r="C43" s="1"/>
+      <c r="E43" s="15"/>
+    </row>
+    <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="17"/>
+      <c r="C44" s="1"/>
+      <c r="E44" s="15"/>
     </row>
     <row r="45" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="26">
-        <v>1</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="26">
-        <v>2</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>48</v>
+      <c r="A45" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="26">
-        <v>3</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="26">
-        <v>4</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E48" s="17"/>
-    </row>
-    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="26">
-        <v>5</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E49" s="17"/>
-    </row>
-    <row r="50" spans="1:8" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="1"/>
-    </row>
-    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
-        <v>14</v>
+      <c r="A47" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="2" t="s">
+    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:8" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="1"/>
-    </row>
-    <row r="96" spans="1:8" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="1"/>
-    </row>
-    <row r="118" spans="1:8" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="2"/>
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-      <c r="H118" s="1"/>
-    </row>
-    <row r="152" spans="13:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="M152" s="27"/>
+    <row r="55" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="79" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="1"/>
+    </row>
+    <row r="101" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="1"/>
+    </row>
+    <row r="123" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="2"/>
+      <c r="G123" s="2"/>
+      <c r="H123" s="1"/>
+    </row>
+    <row r="157" spans="13:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M157" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B25:D25"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B18:D18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/RFQ Generator Beta Version/Templates/OP TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/OP TEMPLATE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274897ED-B03F-4048-A87D-7BC8D1D8D676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49445C40-4F17-433A-92D8-E22642AC0090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2DA8C3B9-7BBA-43E4-97CE-AECDC4D9C533}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="COMMERCIAL." sheetId="32" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'COMMERCIAL.'!$A$1:$H$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'COMMERCIAL.'!$A$1:$H$53</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'COMMERCIAL.'!$1:$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
   <si>
     <t>:</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Qty</t>
   </si>
   <si>
-    <t>GRAND TOTAL</t>
-  </si>
-  <si>
     <t>Price/s quoted above is/are in Ringgit Malaysia</t>
   </si>
   <si>
@@ -177,18 +174,6 @@
     <t>total_price</t>
   </si>
   <si>
-    <t>SUBTOTAL</t>
-  </si>
-  <si>
-    <t>DISCOUNT</t>
-  </si>
-  <si>
-    <t>_discount</t>
-  </si>
-  <si>
-    <t>summary_total_price</t>
-  </si>
-  <si>
     <t>_validity</t>
   </si>
   <si>
@@ -196,6 +181,9 @@
   </si>
   <si>
     <t>delivery_term</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -271,7 +259,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -357,15 +345,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -402,6 +381,58 @@
       </left>
       <right/>
       <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -418,7 +449,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -437,7 +468,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -451,60 +481,64 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="5" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="5" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="5" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -514,44 +548,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -656,13 +663,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>144780</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1017,7 +1024,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1991A9DC-37E5-4BE6-A90B-E8557E5F8471}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AW157"/>
+  <dimension ref="A1:AW155"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" style="2" customWidth="1"/>
@@ -1087,14 +1094,14 @@
     <row r="2" spans="1:49" ht="26.25" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="D2" s="15" t="s">
-        <v>19</v>
+      <c r="D2" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="31"/>
+      <c r="G2" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="24"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -1134,7 +1141,7 @@
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="D3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1"/>
       <c r="M3" s="1"/>
@@ -1176,7 +1183,7 @@
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" s="1"/>
       <c r="M4" s="1"/>
@@ -1216,7 +1223,7 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="D5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" s="1"/>
       <c r="M5" s="1"/>
@@ -1293,7 +1300,7 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="D7" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1"/>
       <c r="M7" s="1"/>
@@ -1333,7 +1340,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="D8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" s="1"/>
       <c r="M8" s="1"/>
@@ -1445,23 +1452,23 @@
     </row>
     <row r="11" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
-      <c r="B11" s="17" t="s">
-        <v>29</v>
+      <c r="B11" s="15" t="s">
+        <v>28</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>29</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -1498,14 +1505,14 @@
     </row>
     <row r="12" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
-      <c r="E12" s="17" t="s">
-        <v>31</v>
+      <c r="E12" s="15" t="s">
+        <v>30</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -1543,14 +1550,14 @@
     <row r="13" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="3"/>
-      <c r="E13" s="17" t="s">
-        <v>32</v>
+      <c r="E13" s="15" t="s">
+        <v>31</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -1686,16 +1693,16 @@
       <c r="AW15" s="1"/>
     </row>
     <row r="16" spans="1:49" s="5" customFormat="1" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
+      <c r="A16" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
@@ -1791,128 +1798,105 @@
     </row>
     <row r="18" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="38"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="37"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
-      <c r="H18" s="9"/>
+      <c r="H18" s="8"/>
     </row>
     <row r="19" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="19" t="s">
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="F19" s="44" t="s">
+      <c r="F19" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="H19" s="19" t="s">
+    </row>
+    <row r="20" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="10"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="12"/>
+    </row>
+    <row r="21" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="13"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="22"/>
+    </row>
+    <row r="22" spans="1:49" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="20" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="11"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="13"/>
-    </row>
-    <row r="21" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="14"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="27"/>
-    </row>
-    <row r="22" spans="1:49" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="10" t="s">
+      <c r="B22" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="C22" s="30"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="46"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="10" t="s">
+      <c r="F22" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="G22" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="G22" s="24" t="s">
+      <c r="H22" s="21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="10"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="19"/>
+    </row>
+    <row r="24" spans="1:49" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="38"/>
+      <c r="B24" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="H22" s="25" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="11"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="21"/>
-    </row>
-    <row r="24" spans="1:49" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="16"/>
-      <c r="B24" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:49" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="10"/>
-      <c r="B25" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:49" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="11"/>
-      <c r="B26" s="49" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="50"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="52" t="s">
-        <v>49</v>
+    </row>
+    <row r="27" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1931,160 +1915,153 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
-        <v>24</v>
+      <c r="A35" s="15"/>
+      <c r="B35" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="15">
+        <v>1</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="17"/>
+      <c r="A37" s="15">
+        <v>2</v>
+      </c>
       <c r="B37" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="17">
-        <v>1</v>
+      <c r="A38" s="15">
+        <v>3</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="15">
+        <v>4</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="17">
-        <v>2</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="17">
-        <v>3</v>
+        <v>47</v>
+      </c>
+      <c r="E39" s="14"/>
+    </row>
+    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="15">
+        <v>5</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>20</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="E40" s="14"/>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="17">
-        <v>4</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E41" s="15"/>
+      <c r="A41" s="15"/>
+      <c r="C41" s="1"/>
+      <c r="E41" s="14"/>
     </row>
     <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="17">
-        <v>5</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E42" s="15"/>
-    </row>
-    <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="17"/>
-      <c r="C43" s="1"/>
-      <c r="E43" s="15"/>
-    </row>
-    <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="17"/>
-      <c r="C44" s="1"/>
-      <c r="E44" s="15"/>
+      <c r="A42" s="15"/>
+      <c r="C42" s="1"/>
+      <c r="E42" s="14"/>
+    </row>
+    <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="45" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="2" t="s">
+    <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="1"/>
-    </row>
-    <row r="79" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="1"/>
-    </row>
-    <row r="101" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="1"/>
-    </row>
-    <row r="123" spans="1:8" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="2"/>
-      <c r="B123" s="2"/>
-      <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
-      <c r="E123" s="2"/>
-      <c r="F123" s="2"/>
-      <c r="G123" s="2"/>
-      <c r="H123" s="1"/>
-    </row>
-    <row r="157" spans="13:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="M157" s="18"/>
+    <row r="53" spans="1:8" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="77" spans="1:8" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="1"/>
+    </row>
+    <row r="99" spans="1:8" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="1"/>
+    </row>
+    <row r="121" spans="1:8" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A121" s="2"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+      <c r="H121" s="1"/>
+    </row>
+    <row r="155" spans="13:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M155" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="8">
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="B19:D19"/>
